--- a/停電作業計画書/停電作業計画書（第3回_整備格納庫）.xlsx
+++ b/停電作業計画書/停電作業計画書（第3回_整備格納庫）.xlsx
@@ -408,7 +408,7 @@
       <row>18</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="4762500" cy="8191500"/>
+    <ext cx="4762500" cy="8039100"/>
     <pic>
       <nvPicPr>
         <cNvPr id="3" name="Image 3" descr="Picture"/>
@@ -15592,14 +15592,14 @@
     <row r="17" ht="20" customHeight="1">
       <c r="A17" s="31" t="inlineStr">
         <is>
-          <t>【改修範囲（単線結線図　改修後）―　㈱別川製作所　製作仕様書（A7EC0541）P-1　より】</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="30.6" customHeight="1">
+          <t>【ED-07　整備格納庫　単線結線図　改修後　―　改修範囲（太線部）を赤線で表示】</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="43.3" customHeight="1">
       <c r="A18" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">　雲形（★1～★7）で囲まれた部分が改造範囲を示す。縮小図のため詳細は原図（A3）による。図は左が上となるよう90°回転して掲載。</t>
+          <t xml:space="preserve">　ED-07注記1）「図中、太線部の高圧機器、継電器及び高圧母線を新設する。」の太線部を赤線で表示した（赤線＝改修範囲、黒線＝既設）。縮小図のため詳細は原図（A3）による。図は左が上となるよう90°回転して掲載。機器の定格（PF・FBU等）は製作仕様書（A7EC0541）による。</t>
         </is>
       </c>
     </row>
@@ -15613,7 +15613,7 @@
     <row r="26" ht="60" customHeight="1"/>
     <row r="27" ht="60" customHeight="1"/>
     <row r="28" ht="60" customHeight="1"/>
-    <row r="29" ht="51" customHeight="1"/>
+    <row r="29" ht="39" customHeight="1"/>
     <row r="30" ht="20.6" customHeight="1">
       <c r="A30" s="15" t="inlineStr">
         <is>
